--- a/main/ig/ValueSet-fr-mp-dose-form.xlsx
+++ b/main/ig/ValueSet-fr-mp-dose-form.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-11-05T08:58:38+00:00</t>
+    <t>2025-11-07T10:40:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-mp-dose-form.xlsx
+++ b/main/ig/ValueSet-fr-mp-dose-form.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-11-07T10:40:44+00:00</t>
+    <t>2025-11-25T08:22:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-mp-dose-form.xlsx
+++ b/main/ig/ValueSet-fr-mp-dose-form.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-11-25T08:22:04+00:00</t>
+    <t>2026-01-16T18:04:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-mp-dose-form.xlsx
+++ b/main/ig/ValueSet-fr-mp-dose-form.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-16T18:04:25+00:00</t>
+    <t>2026-01-23T16:54:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-mp-dose-form.xlsx
+++ b/main/ig/ValueSet-fr-mp-dose-form.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-23T16:54:57+00:00</t>
+    <t>2026-01-23T16:56:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-mp-dose-form.xlsx
+++ b/main/ig/ValueSet-fr-mp-dose-form.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-23T16:56:48+00:00</t>
+    <t>2026-02-09T09:37:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-mp-dose-form.xlsx
+++ b/main/ig/ValueSet-fr-mp-dose-form.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-09T09:37:19+00:00</t>
+    <t>2026-02-23T11:15:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-mp-dose-form.xlsx
+++ b/main/ig/ValueSet-fr-mp-dose-form.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-23T11:15:05+00:00</t>
+    <t>2026-04-02T15:16:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-mp-dose-form.xlsx
+++ b/main/ig/ValueSet-fr-mp-dose-form.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-02T15:16:30+00:00</t>
+    <t>2026-05-04T12:24:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-mp-dose-form.xlsx
+++ b/main/ig/ValueSet-fr-mp-dose-form.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-04T12:24:40+00:00</t>
+    <t>2026-05-04T13:30:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -81,7 +81,7 @@
     <t>Jurisdiction</t>
   </si>
   <si>
-    <t>FRANCE</t>
+    <t>France (la)</t>
   </si>
   <si>
     <t>Description</t>

--- a/main/ig/ValueSet-fr-mp-dose-form.xlsx
+++ b/main/ig/ValueSet-fr-mp-dose-form.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-04T13:30:13+00:00</t>
+    <t>2026-05-06T13:16:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-mp-dose-form.xlsx
+++ b/main/ig/ValueSet-fr-mp-dose-form.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0</t>
+    <t>1.1.0-ballot</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-06T13:16:54+00:00</t>
+    <t>2026-05-10T16:39:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-mp-dose-form.xlsx
+++ b/main/ig/ValueSet-fr-mp-dose-form.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-10T16:39:38+00:00</t>
+    <t>2026-05-10T16:47:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-mp-dose-form.xlsx
+++ b/main/ig/ValueSet-fr-mp-dose-form.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-10T16:47:08+00:00</t>
+    <t>2026-05-11T06:03:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-mp-dose-form.xlsx
+++ b/main/ig/ValueSet-fr-mp-dose-form.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-11T06:03:48+00:00</t>
+    <t>2026-05-11T06:11:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-mp-dose-form.xlsx
+++ b/main/ig/ValueSet-fr-mp-dose-form.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-11T06:11:37+00:00</t>
+    <t>2026-07-10T14:23:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
